--- a/poker/resources/sample/Texas.xlsx
+++ b/poker/resources/sample/Texas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="824"/>
+    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="824"/>
   </bookViews>
   <sheets>
     <sheet name="Texas" sheetId="47" r:id="rId1"/>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="42">
   <si>
     <t>id</t>
   </si>
@@ -460,12 +460,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1331,10 +1331,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="6"/>
+  <dimension ref="A1:R10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="2"/>
+    <col min="1" max="1" width="10.375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
     <col min="3" max="3" width="17.5" style="2" customWidth="1"/>
     <col min="4" max="4" width="9.625" style="2" customWidth="1"/>
@@ -1672,6 +1672,165 @@
         <v>41</v>
       </c>
     </row>
+    <row r="8" spans="1:18">
+      <c r="A8" s="2">
+        <v>30020010</v>
+      </c>
+      <c r="B8" s="1">
+        <v>300200</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>50</v>
+      </c>
+      <c r="J8" s="2">
+        <v>100</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L8" s="2">
+        <v>2</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N8" s="2">
+        <v>100002</v>
+      </c>
+      <c r="P8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>0</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" s="2">
+        <v>30020011</v>
+      </c>
+      <c r="B9" s="1">
+        <v>300200</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="1">
+        <v>2</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>100</v>
+      </c>
+      <c r="J9" s="2">
+        <v>200</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L9" s="2">
+        <v>2</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N9" s="2">
+        <v>100002</v>
+      </c>
+      <c r="P9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="2">
+        <v>30020012</v>
+      </c>
+      <c r="B10" s="1">
+        <v>300200</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="1">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="2">
+        <v>60000000</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>200</v>
+      </c>
+      <c r="J10" s="2">
+        <v>400</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L10" s="2">
+        <v>2</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N10" s="2">
+        <v>100002</v>
+      </c>
+      <c r="P10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:R7" etc:filterBottomFollowUsedRange="0">
     <extLst/>

--- a/poker/resources/sample/Texas.xlsx
+++ b/poker/resources/sample/Texas.xlsx
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="42">
   <si>
     <t>id</t>
   </si>
@@ -460,12 +460,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1331,10 +1331,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelRow="6"/>
+  <dimension ref="A1:R10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="1" width="9" style="2"/>
+    <col min="1" max="1" width="10.375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
     <col min="3" max="3" width="17.5" style="2" customWidth="1"/>
     <col min="4" max="4" width="9.625" style="2" customWidth="1"/>
@@ -1460,7 +1460,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" hidden="1" spans="1:17">
+    <row r="3" s="1" customFormat="1" spans="1:17">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" hidden="1" spans="5:5">
+    <row r="4" s="1" customFormat="1" spans="5:5">
       <c r="E4" s="7"/>
     </row>
     <row r="5" spans="1:18">
@@ -1669,6 +1669,165 @@
         <v>0</v>
       </c>
       <c r="R7" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
+      <c r="A8" s="2">
+        <v>30020010</v>
+      </c>
+      <c r="B8" s="1">
+        <v>300200</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2">
+        <v>2000000</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G8" s="2">
+        <v>3000000</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>50</v>
+      </c>
+      <c r="J8" s="2">
+        <v>100</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L8" s="2">
+        <v>2</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N8" s="2">
+        <v>100002</v>
+      </c>
+      <c r="P8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>0</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" s="2">
+        <v>30020011</v>
+      </c>
+      <c r="B9" s="1">
+        <v>300200</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="1">
+        <v>2</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4000000</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2">
+        <v>100</v>
+      </c>
+      <c r="J9" s="2">
+        <v>200</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L9" s="2">
+        <v>2</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N9" s="2">
+        <v>100002</v>
+      </c>
+      <c r="P9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="2">
+        <v>30020012</v>
+      </c>
+      <c r="B10" s="1">
+        <v>300200</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="1">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2">
+        <v>20000000</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G10" s="2">
+        <v>60000000</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
+      </c>
+      <c r="I10" s="2">
+        <v>200</v>
+      </c>
+      <c r="J10" s="2">
+        <v>400</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="L10" s="2">
+        <v>2</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N10" s="2">
+        <v>100002</v>
+      </c>
+      <c r="P10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="2">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1" t="s">
         <v>41</v>
       </c>
     </row>

--- a/poker/resources/sample/Texas.xlsx
+++ b/poker/resources/sample/Texas.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Texas" sheetId="47" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Texas!$B$1:$R$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Texas!$B$1:$T$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +60,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="1">
+    <comment ref="H1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -73,7 +73,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="1">
+    <comment ref="J1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -95,19 +95,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="1">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>单位：K</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="1">
+    <comment ref="K1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -127,12 +115,24 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
+          <t>单位：K</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
           <t>1 先跟再加
 2 直接加</t>
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="2">
+    <comment ref="Q1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -152,7 +152,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="46">
   <si>
     <t>id</t>
   </si>
@@ -169,6 +169,12 @@
     <t>默认带入金币</t>
   </si>
   <si>
+    <t>准备阶段时间（毫秒）</t>
+  </si>
+  <si>
+    <t>请离房间（毫秒）</t>
+  </si>
+  <si>
     <t>补齐金币</t>
   </si>
   <si>
@@ -227,6 +233,12 @@
   </si>
   <si>
     <t>coinsNum</t>
+  </si>
+  <si>
+    <t>preparationTime</t>
+  </si>
+  <si>
+    <t>escTime</t>
   </si>
   <si>
     <t>bankruptcoin</t>
@@ -460,12 +472,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -988,11 +1000,11 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1331,30 +1343,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:T10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
     <col min="3" max="3" width="17.5" style="2" customWidth="1"/>
     <col min="4" max="4" width="9.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="28.625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="52" style="2" customWidth="1"/>
-    <col min="7" max="7" width="19.725" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.25" style="2" customWidth="1"/>
-    <col min="9" max="10" width="9" style="2"/>
-    <col min="11" max="11" width="16.875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="19.75" style="2" customWidth="1"/>
-    <col min="13" max="13" width="22.5" style="2" customWidth="1"/>
-    <col min="14" max="14" width="9" style="2"/>
-    <col min="15" max="15" width="24.75" style="2" customWidth="1"/>
-    <col min="16" max="16" width="11.25" style="2" customWidth="1"/>
-    <col min="17" max="17" width="9.25" style="2" customWidth="1"/>
-    <col min="18" max="18" width="15" style="2" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="2"/>
+    <col min="5" max="7" width="28.625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="52" style="2" customWidth="1"/>
+    <col min="9" max="9" width="19.725" style="2" customWidth="1"/>
+    <col min="10" max="10" width="9.25" style="2" customWidth="1"/>
+    <col min="11" max="12" width="9" style="2"/>
+    <col min="13" max="13" width="16.875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="19.75" style="2" customWidth="1"/>
+    <col min="15" max="15" width="22.5" style="2" customWidth="1"/>
+    <col min="16" max="16" width="9" style="2"/>
+    <col min="17" max="17" width="24.75" style="2" customWidth="1"/>
+    <col min="18" max="18" width="11.25" style="2" customWidth="1"/>
+    <col min="19" max="19" width="9.25" style="2" customWidth="1"/>
+    <col min="20" max="20" width="15" style="2" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:20">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1370,150 +1382,170 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="8" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:17">
+    <row r="2" s="1" customFormat="1" spans="1:19">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="1" t="s">
-        <v>18</v>
-      </c>
       <c r="O2" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="P2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Q2" s="1" t="s">
-        <v>18</v>
+      <c r="R2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:17">
+    <row r="3" s="1" customFormat="1" spans="1:19">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="5:5">
-      <c r="E4" s="7"/>
+    <row r="4" s="1" customFormat="1" spans="5:7">
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:20">
       <c r="A5" s="2">
         <v>3002001</v>
       </c>
@@ -1521,7 +1553,7 @@
         <v>300200</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -1529,44 +1561,50 @@
       <c r="E5" s="2">
         <v>2000000</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>38</v>
+      <c r="F5" s="2">
+        <v>8000</v>
       </c>
       <c r="G5" s="2">
+        <v>60000</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="2">
         <v>3000000</v>
       </c>
-      <c r="H5" s="2">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
-      <c r="I5" s="2">
+      <c r="K5" s="2">
         <v>50</v>
       </c>
-      <c r="J5" s="2">
+      <c r="L5" s="2">
         <v>100</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L5" s="2">
+      <c r="M5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" s="2">
         <v>2</v>
       </c>
-      <c r="M5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N5" s="2">
+      <c r="O5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P5" s="2">
         <v>100002</v>
       </c>
-      <c r="P5" s="2" t="b">
+      <c r="R5" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="S5" s="2">
         <v>0</v>
       </c>
-      <c r="R5" s="1" t="s">
-        <v>41</v>
+      <c r="T5" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:20">
       <c r="A6" s="2">
         <v>3002002</v>
       </c>
@@ -1574,7 +1612,7 @@
         <v>300200</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
@@ -1582,44 +1620,50 @@
       <c r="E6" s="2">
         <v>4000000</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>38</v>
+      <c r="F6" s="2">
+        <v>8000</v>
       </c>
       <c r="G6" s="2">
+        <v>60000</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" s="2">
         <v>6000000</v>
       </c>
-      <c r="H6" s="2">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
-      <c r="I6" s="2">
+      <c r="K6" s="2">
         <v>100</v>
       </c>
-      <c r="J6" s="2">
+      <c r="L6" s="2">
         <v>200</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L6" s="2">
+      <c r="M6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N6" s="2">
         <v>2</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N6" s="2">
+      <c r="O6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P6" s="2">
         <v>100002</v>
       </c>
-      <c r="P6" s="2" t="b">
+      <c r="R6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="S6" s="2">
         <v>0</v>
       </c>
-      <c r="R6" s="1" t="s">
-        <v>41</v>
+      <c r="T6" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:20">
       <c r="A7" s="2">
         <v>3002003</v>
       </c>
@@ -1627,7 +1671,7 @@
         <v>300200</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -1635,44 +1679,50 @@
       <c r="E7" s="2">
         <v>20000000</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>38</v>
+      <c r="F7" s="2">
+        <v>8000</v>
       </c>
       <c r="G7" s="2">
+        <v>60000</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7" s="2">
         <v>60000000</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>200</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>400</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N7" s="2">
         <v>2</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P7" s="2">
         <v>100002</v>
       </c>
-      <c r="P7" s="2" t="b">
+      <c r="R7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>0</v>
       </c>
-      <c r="R7" s="1" t="s">
-        <v>41</v>
+      <c r="T7" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:20">
       <c r="A8" s="2">
         <v>30020010</v>
       </c>
@@ -1680,52 +1730,58 @@
         <v>300200</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
       </c>
       <c r="E8" s="2">
-        <v>2000000</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>38</v>
+        <v>2000</v>
+      </c>
+      <c r="F8" s="2">
+        <v>8000</v>
       </c>
       <c r="G8" s="2">
-        <v>3000000</v>
-      </c>
-      <c r="H8" s="2">
+        <v>60000</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8" s="2">
+        <v>3000</v>
+      </c>
+      <c r="J8" s="2">
         <v>0</v>
       </c>
-      <c r="I8" s="2">
-        <v>50</v>
-      </c>
-      <c r="J8" s="2">
-        <v>100</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>39</v>
+      <c r="K8" s="2">
+        <v>1</v>
       </c>
       <c r="L8" s="2">
         <v>2</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="N8" s="2">
+        <v>2</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P8" s="2">
         <v>100002</v>
       </c>
-      <c r="P8" s="2" t="b">
+      <c r="R8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="S8" s="2">
         <v>0</v>
       </c>
-      <c r="R8" s="1" t="s">
-        <v>41</v>
+      <c r="T8" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:20">
       <c r="A9" s="2">
         <v>30020011</v>
       </c>
@@ -1733,52 +1789,58 @@
         <v>300200</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
       </c>
       <c r="E9" s="2">
-        <v>4000000</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>38</v>
+        <v>8000</v>
+      </c>
+      <c r="F9" s="2">
+        <v>8000</v>
       </c>
       <c r="G9" s="2">
-        <v>6000000</v>
-      </c>
-      <c r="H9" s="2">
+        <v>60000</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I9" s="2">
+        <v>12000</v>
+      </c>
+      <c r="J9" s="2">
         <v>0</v>
       </c>
-      <c r="I9" s="2">
-        <v>100</v>
-      </c>
-      <c r="J9" s="2">
-        <v>200</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>39</v>
+      <c r="K9" s="2">
+        <v>2</v>
       </c>
       <c r="L9" s="2">
+        <v>4</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N9" s="2">
         <v>2</v>
       </c>
-      <c r="M9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N9" s="2">
+      <c r="O9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P9" s="2">
         <v>100002</v>
       </c>
-      <c r="P9" s="2" t="b">
+      <c r="R9" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="S9" s="2">
         <v>0</v>
       </c>
-      <c r="R9" s="1" t="s">
-        <v>41</v>
+      <c r="T9" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:20">
       <c r="A10" s="2">
         <v>30020012</v>
       </c>
@@ -1786,53 +1848,59 @@
         <v>300200</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
       </c>
       <c r="E10" s="2">
-        <v>20000000</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>38</v>
+        <v>20000</v>
+      </c>
+      <c r="F10" s="2">
+        <v>8000</v>
       </c>
       <c r="G10" s="2">
-        <v>60000000</v>
-      </c>
-      <c r="H10" s="2">
+        <v>60000</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="I10" s="2">
+        <v>60000</v>
+      </c>
+      <c r="J10" s="2">
         <v>0</v>
       </c>
-      <c r="I10" s="2">
-        <v>200</v>
-      </c>
-      <c r="J10" s="2">
-        <v>400</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>39</v>
+      <c r="K10" s="2">
+        <v>4</v>
       </c>
       <c r="L10" s="2">
+        <v>8</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N10" s="2">
         <v>2</v>
       </c>
-      <c r="M10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N10" s="2">
+      <c r="O10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="P10" s="2">
         <v>100002</v>
       </c>
-      <c r="P10" s="2" t="b">
+      <c r="R10" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="S10" s="2">
         <v>0</v>
       </c>
-      <c r="R10" s="1" t="s">
-        <v>41</v>
+      <c r="T10" s="1" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:R7" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:T10" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/poker/resources/sample/Texas.xlsx
+++ b/poker/resources/sample/Texas.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Texas" sheetId="47" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Texas!$B$1:$T$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Texas!$B$1:$R$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -64,19 +64,6 @@
       <text>
         <r>
           <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>玩家破产后可带入的金币
-X倍底注</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J1" authorId="1">
-      <text>
-        <r>
-          <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
@@ -95,7 +82,19 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="1">
+    <comment ref="I1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>单位：K</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -115,24 +114,12 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>单位：K</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="1">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
           <t>1 先跟再加
 2 直接加</t>
         </r>
       </text>
     </comment>
-    <comment ref="Q1" authorId="2">
+    <comment ref="O1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -152,7 +139,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="41">
   <si>
     <t>id</t>
   </si>
@@ -166,18 +153,12 @@
     <t>房间类型</t>
   </si>
   <si>
-    <t>默认带入金币</t>
-  </si>
-  <si>
-    <t>准备阶段时间（毫秒）</t>
+    <t>默认入座金币</t>
   </si>
   <si>
     <t>请离房间（毫秒）</t>
   </si>
   <si>
-    <t>补齐金币</t>
-  </si>
-  <si>
     <t>上桌金额</t>
   </si>
   <si>
@@ -235,15 +216,9 @@
     <t>coinsNum</t>
   </si>
   <si>
-    <t>preparationTime</t>
-  </si>
-  <si>
     <t>escTime</t>
   </si>
   <si>
-    <t>bankruptcoin</t>
-  </si>
-  <si>
     <t>tablecoin</t>
   </si>
   <si>
@@ -278,9 +253,6 @@
   </si>
   <si>
     <t>欢乐德州</t>
-  </si>
-  <si>
-    <t>1;2;3;4;5;6;7;8;9;10</t>
   </si>
   <si>
     <t>1;3;4;5</t>
@@ -1000,11 +972,11 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1343,30 +1315,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
     <col min="3" max="3" width="17.5" style="2" customWidth="1"/>
     <col min="4" max="4" width="9.625" style="2" customWidth="1"/>
-    <col min="5" max="7" width="28.625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="52" style="2" customWidth="1"/>
-    <col min="9" max="9" width="19.725" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9.25" style="2" customWidth="1"/>
-    <col min="11" max="12" width="9" style="2"/>
-    <col min="13" max="13" width="16.875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="19.75" style="2" customWidth="1"/>
-    <col min="15" max="15" width="22.5" style="2" customWidth="1"/>
-    <col min="16" max="16" width="9" style="2"/>
-    <col min="17" max="17" width="24.75" style="2" customWidth="1"/>
-    <col min="18" max="18" width="11.25" style="2" customWidth="1"/>
-    <col min="19" max="19" width="9.25" style="2" customWidth="1"/>
-    <col min="20" max="20" width="15" style="2" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="2"/>
+    <col min="5" max="6" width="28.625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="19.725" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9.25" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9" style="2"/>
+    <col min="10" max="10" width="9.25" style="2"/>
+    <col min="11" max="11" width="16.875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="19.75" style="2" customWidth="1"/>
+    <col min="13" max="13" width="22.5" style="2" customWidth="1"/>
+    <col min="14" max="14" width="9" style="2"/>
+    <col min="15" max="15" width="24.75" style="2" customWidth="1"/>
+    <col min="16" max="16" width="11.25" style="2" customWidth="1"/>
+    <col min="17" max="17" width="9.25" style="2" customWidth="1"/>
+    <col min="18" max="18" width="15" style="2" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:18">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1385,167 +1357,148 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="P1" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="Q1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="9" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:17">
+      <c r="A2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="L2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:19">
-      <c r="A2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:19">
+    <row r="3" s="1" customFormat="1" spans="1:17">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="P3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>40</v>
-      </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="5:7">
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
+    <row r="4" s="1" customFormat="1" spans="5:6">
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:18">
       <c r="A5" s="2">
         <v>3002001</v>
       </c>
@@ -1553,7 +1506,7 @@
         <v>300200</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -1562,49 +1515,46 @@
         <v>2000000</v>
       </c>
       <c r="F5" s="2">
-        <v>8000</v>
+        <v>60000</v>
       </c>
       <c r="G5" s="2">
-        <v>60000</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>42</v>
+        <f t="shared" ref="G5:G10" si="0">E5*2</f>
+        <v>4000000</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>3000000</v>
+        <f t="shared" ref="I5:I10" si="1">J5/2</f>
+        <v>50000</v>
       </c>
       <c r="J5" s="2">
+        <f t="shared" ref="J5:J10" si="2">E5/20</f>
+        <v>100000</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5" s="2">
+        <v>2</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N5" s="2">
+        <v>100002</v>
+      </c>
+      <c r="P5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="2">
         <v>0</v>
       </c>
-      <c r="K5" s="2">
-        <v>50</v>
-      </c>
-      <c r="L5" s="2">
-        <v>100</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N5" s="2">
-        <v>2</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P5" s="2">
-        <v>100002</v>
-      </c>
-      <c r="R5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="S5" s="2">
-        <v>0</v>
-      </c>
-      <c r="T5" s="1" t="s">
-        <v>45</v>
+      <c r="R5" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:18">
       <c r="A6" s="2">
         <v>3002002</v>
       </c>
@@ -1612,7 +1562,7 @@
         <v>300200</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
@@ -1621,49 +1571,46 @@
         <v>4000000</v>
       </c>
       <c r="F6" s="2">
-        <v>8000</v>
+        <v>60000</v>
       </c>
       <c r="G6" s="2">
-        <v>60000</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>42</v>
+        <f t="shared" si="0"/>
+        <v>8000000</v>
+      </c>
+      <c r="H6" s="2">
+        <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>6000000</v>
+        <f t="shared" si="1"/>
+        <v>100000</v>
       </c>
       <c r="J6" s="2">
+        <f t="shared" si="2"/>
+        <v>200000</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L6" s="2">
+        <v>2</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N6" s="2">
+        <v>100002</v>
+      </c>
+      <c r="P6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="2">
         <v>0</v>
       </c>
-      <c r="K6" s="2">
-        <v>100</v>
-      </c>
-      <c r="L6" s="2">
-        <v>200</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N6" s="2">
-        <v>2</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P6" s="2">
-        <v>100002</v>
-      </c>
-      <c r="R6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="S6" s="2">
-        <v>0</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>45</v>
+      <c r="R6" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:18">
       <c r="A7" s="2">
         <v>3002003</v>
       </c>
@@ -1671,7 +1618,7 @@
         <v>300200</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -1680,49 +1627,46 @@
         <v>20000000</v>
       </c>
       <c r="F7" s="2">
-        <v>8000</v>
+        <v>60000</v>
       </c>
       <c r="G7" s="2">
-        <v>60000</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>42</v>
+        <f t="shared" si="0"/>
+        <v>40000000</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
       </c>
       <c r="I7" s="2">
-        <v>60000000</v>
+        <f t="shared" si="1"/>
+        <v>500000</v>
       </c>
       <c r="J7" s="2">
+        <f t="shared" si="2"/>
+        <v>1000000</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L7" s="2">
+        <v>2</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N7" s="2">
+        <v>100002</v>
+      </c>
+      <c r="P7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="2">
         <v>0</v>
       </c>
-      <c r="K7" s="2">
-        <v>200</v>
-      </c>
-      <c r="L7" s="2">
-        <v>400</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N7" s="2">
-        <v>2</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P7" s="2">
-        <v>100002</v>
-      </c>
-      <c r="R7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="S7" s="2">
-        <v>0</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>45</v>
+      <c r="R7" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:20">
+    <row r="8" spans="1:18">
       <c r="A8" s="2">
         <v>30020010</v>
       </c>
@@ -1730,7 +1674,7 @@
         <v>300200</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -1739,49 +1683,46 @@
         <v>2000</v>
       </c>
       <c r="F8" s="2">
-        <v>8000</v>
+        <v>60000</v>
       </c>
       <c r="G8" s="2">
-        <v>60000</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>42</v>
+        <f t="shared" si="0"/>
+        <v>4000</v>
+      </c>
+      <c r="H8" s="2">
+        <v>0</v>
       </c>
       <c r="I8" s="2">
-        <v>3000</v>
+        <f t="shared" si="1"/>
+        <v>50</v>
       </c>
       <c r="J8" s="2">
-        <v>0</v>
-      </c>
-      <c r="K8" s="2">
-        <v>1</v>
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="L8" s="2">
         <v>2</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="N8" s="2">
-        <v>2</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P8" s="2">
         <v>100002</v>
       </c>
-      <c r="R8" s="2" t="b">
+      <c r="P8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="S8" s="2">
+      <c r="Q8" s="2">
         <v>0</v>
       </c>
-      <c r="T8" s="1" t="s">
-        <v>45</v>
+      <c r="R8" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:18">
       <c r="A9" s="2">
         <v>30020011</v>
       </c>
@@ -1789,7 +1730,7 @@
         <v>300200</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -1798,49 +1739,46 @@
         <v>8000</v>
       </c>
       <c r="F9" s="2">
-        <v>8000</v>
+        <v>60000</v>
       </c>
       <c r="G9" s="2">
-        <v>60000</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>42</v>
+        <f t="shared" si="0"/>
+        <v>16000</v>
+      </c>
+      <c r="H9" s="2">
+        <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>12000</v>
+        <f t="shared" si="1"/>
+        <v>200</v>
       </c>
       <c r="J9" s="2">
+        <f t="shared" si="2"/>
+        <v>400</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L9" s="2">
+        <v>2</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N9" s="2">
+        <v>100002</v>
+      </c>
+      <c r="P9" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="2">
         <v>0</v>
       </c>
-      <c r="K9" s="2">
-        <v>2</v>
-      </c>
-      <c r="L9" s="2">
-        <v>4</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N9" s="2">
-        <v>2</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P9" s="2">
-        <v>100002</v>
-      </c>
-      <c r="R9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="S9" s="2">
-        <v>0</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>45</v>
+      <c r="R9" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:18">
       <c r="A10" s="2">
         <v>30020012</v>
       </c>
@@ -1848,7 +1786,7 @@
         <v>300200</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -1857,50 +1795,47 @@
         <v>20000</v>
       </c>
       <c r="F10" s="2">
-        <v>8000</v>
+        <v>60000</v>
       </c>
       <c r="G10" s="2">
-        <v>60000</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>42</v>
+        <f t="shared" si="0"/>
+        <v>40000</v>
+      </c>
+      <c r="H10" s="2">
+        <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>60000</v>
+        <f t="shared" si="1"/>
+        <v>500</v>
       </c>
       <c r="J10" s="2">
+        <f t="shared" si="2"/>
+        <v>1000</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L10" s="2">
+        <v>2</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N10" s="2">
+        <v>100002</v>
+      </c>
+      <c r="P10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="2">
         <v>0</v>
       </c>
-      <c r="K10" s="2">
-        <v>4</v>
-      </c>
-      <c r="L10" s="2">
-        <v>8</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N10" s="2">
-        <v>2</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="P10" s="2">
-        <v>100002</v>
-      </c>
-      <c r="R10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="S10" s="2">
-        <v>0</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>45</v>
+      <c r="R10" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:T10" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:R10" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/poker/resources/sample/Texas.xlsx
+++ b/poker/resources/sample/Texas.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Texas" sheetId="47" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Texas!$B$1:$R$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Texas!$B$1:$S$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +60,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="1">
+    <comment ref="I1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -82,18 +82,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="1">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>单位：K</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="J1" authorId="1">
       <text>
         <r>
@@ -106,7 +94,19 @@
         </r>
       </text>
     </comment>
-    <comment ref="L1" authorId="1">
+    <comment ref="K1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>单位：K</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -119,7 +119,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O1" authorId="2">
+    <comment ref="P1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="43">
   <si>
     <t>id</t>
   </si>
@@ -159,6 +159,9 @@
     <t>请离房间（毫秒）</t>
   </si>
   <si>
+    <t>踢出房间提示</t>
+  </si>
+  <si>
     <t>上桌金额</t>
   </si>
   <si>
@@ -217,6 +220,9 @@
   </si>
   <si>
     <t>escTime</t>
+  </si>
+  <si>
+    <t>escTipText</t>
   </si>
   <si>
     <t>tablecoin</t>
@@ -972,11 +978,11 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1315,30 +1321,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:S10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
     <col min="3" max="3" width="17.5" style="2" customWidth="1"/>
     <col min="4" max="4" width="9.625" style="2" customWidth="1"/>
-    <col min="5" max="6" width="28.625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="19.725" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.25" style="2" customWidth="1"/>
-    <col min="9" max="9" width="9" style="2"/>
-    <col min="10" max="10" width="9.25" style="2"/>
-    <col min="11" max="11" width="16.875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="19.75" style="2" customWidth="1"/>
-    <col min="13" max="13" width="22.5" style="2" customWidth="1"/>
-    <col min="14" max="14" width="9" style="2"/>
-    <col min="15" max="15" width="24.75" style="2" customWidth="1"/>
-    <col min="16" max="16" width="11.25" style="2" customWidth="1"/>
-    <col min="17" max="17" width="9.25" style="2" customWidth="1"/>
-    <col min="18" max="18" width="15" style="2" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="2"/>
+    <col min="5" max="7" width="28.625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="19.725" style="2" customWidth="1"/>
+    <col min="9" max="9" width="9.25" style="2" customWidth="1"/>
+    <col min="10" max="10" width="9" style="2"/>
+    <col min="11" max="11" width="9.25" style="2"/>
+    <col min="12" max="12" width="16.875" style="2" customWidth="1"/>
+    <col min="13" max="13" width="19.75" style="2" customWidth="1"/>
+    <col min="14" max="14" width="22.5" style="2" customWidth="1"/>
+    <col min="15" max="15" width="9" style="2"/>
+    <col min="16" max="16" width="24.75" style="2" customWidth="1"/>
+    <col min="17" max="17" width="11.25" style="2" customWidth="1"/>
+    <col min="18" max="18" width="9.25" style="2" customWidth="1"/>
+    <col min="19" max="19" width="15" style="2" customWidth="1"/>
+    <col min="20" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:19">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1357,148 +1363,158 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="P1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="9" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:17">
+    <row r="2" s="1" customFormat="1" spans="1:18">
       <c r="A2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>19</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:17">
+    <row r="3" s="1" customFormat="1" spans="1:18">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="5:6">
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+    <row r="4" s="1" customFormat="1" spans="5:7">
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:19">
       <c r="A5" s="2">
         <v>3002001</v>
       </c>
@@ -1506,7 +1522,7 @@
         <v>300200</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -1518,43 +1534,46 @@
         <v>60000</v>
       </c>
       <c r="G5" s="2">
-        <f t="shared" ref="G5:G10" si="0">E5*2</f>
+        <v>16008</v>
+      </c>
+      <c r="H5" s="2">
+        <f t="shared" ref="H5:H10" si="0">E5*2</f>
         <v>4000000</v>
       </c>
-      <c r="H5" s="2">
+      <c r="I5" s="2">
         <v>0</v>
       </c>
-      <c r="I5" s="2">
-        <f t="shared" ref="I5:I10" si="1">J5/2</f>
+      <c r="J5" s="2">
+        <f t="shared" ref="J5:J10" si="1">K5/2</f>
         <v>50000</v>
       </c>
-      <c r="J5" s="2">
-        <f t="shared" ref="J5:J10" si="2">E5/20</f>
+      <c r="K5" s="2">
+        <f t="shared" ref="K5:K10" si="2">E5/20</f>
         <v>100000</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L5" s="2">
+      <c r="L5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M5" s="2">
         <v>2</v>
       </c>
-      <c r="M5" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5" s="2">
+      <c r="N5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O5" s="2">
         <v>100002</v>
       </c>
-      <c r="P5" s="2" t="b">
+      <c r="Q5" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="R5" s="2">
         <v>0</v>
       </c>
-      <c r="R5" s="1" t="s">
-        <v>40</v>
+      <c r="S5" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:19">
       <c r="A6" s="2">
         <v>3002002</v>
       </c>
@@ -1562,7 +1581,7 @@
         <v>300200</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
@@ -1574,43 +1593,46 @@
         <v>60000</v>
       </c>
       <c r="G6" s="2">
+        <v>16008</v>
+      </c>
+      <c r="H6" s="2">
         <f t="shared" si="0"/>
         <v>8000000</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <v>0</v>
       </c>
-      <c r="I6" s="2">
+      <c r="J6" s="2">
         <f t="shared" si="1"/>
         <v>100000</v>
       </c>
-      <c r="J6" s="2">
+      <c r="K6" s="2">
         <f t="shared" si="2"/>
         <v>200000</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L6" s="2">
+      <c r="L6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M6" s="2">
         <v>2</v>
       </c>
-      <c r="M6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N6" s="2">
+      <c r="N6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O6" s="2">
         <v>100002</v>
       </c>
-      <c r="P6" s="2" t="b">
+      <c r="Q6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="R6" s="2">
         <v>0</v>
       </c>
-      <c r="R6" s="1" t="s">
-        <v>40</v>
+      <c r="S6" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:19">
       <c r="A7" s="2">
         <v>3002003</v>
       </c>
@@ -1618,7 +1640,7 @@
         <v>300200</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -1630,43 +1652,46 @@
         <v>60000</v>
       </c>
       <c r="G7" s="2">
+        <v>16008</v>
+      </c>
+      <c r="H7" s="2">
         <f t="shared" si="0"/>
         <v>40000000</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>0</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <f t="shared" si="1"/>
         <v>500000</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <f t="shared" si="2"/>
         <v>1000000</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L7" s="2">
+      <c r="L7" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M7" s="2">
         <v>2</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N7" s="2">
+      <c r="N7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O7" s="2">
         <v>100002</v>
       </c>
-      <c r="P7" s="2" t="b">
+      <c r="Q7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>0</v>
       </c>
-      <c r="R7" s="1" t="s">
-        <v>40</v>
+      <c r="S7" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:19">
       <c r="A8" s="2">
         <v>30020010</v>
       </c>
@@ -1674,7 +1699,7 @@
         <v>300200</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -1686,43 +1711,46 @@
         <v>60000</v>
       </c>
       <c r="G8" s="2">
+        <v>16008</v>
+      </c>
+      <c r="H8" s="2">
         <f t="shared" si="0"/>
         <v>4000</v>
       </c>
-      <c r="H8" s="2">
+      <c r="I8" s="2">
         <v>0</v>
       </c>
-      <c r="I8" s="2">
+      <c r="J8" s="2">
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="J8" s="2">
+      <c r="K8" s="2">
         <f t="shared" si="2"/>
         <v>100</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L8" s="2">
+      <c r="L8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M8" s="2">
         <v>2</v>
       </c>
-      <c r="M8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N8" s="2">
+      <c r="N8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O8" s="2">
         <v>100002</v>
       </c>
-      <c r="P8" s="2" t="b">
+      <c r="Q8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="R8" s="2">
         <v>0</v>
       </c>
-      <c r="R8" s="1" t="s">
-        <v>40</v>
+      <c r="S8" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:19">
       <c r="A9" s="2">
         <v>30020011</v>
       </c>
@@ -1730,7 +1758,7 @@
         <v>300200</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -1742,43 +1770,46 @@
         <v>60000</v>
       </c>
       <c r="G9" s="2">
+        <v>16008</v>
+      </c>
+      <c r="H9" s="2">
         <f t="shared" si="0"/>
         <v>16000</v>
       </c>
-      <c r="H9" s="2">
+      <c r="I9" s="2">
         <v>0</v>
       </c>
-      <c r="I9" s="2">
+      <c r="J9" s="2">
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="J9" s="2">
+      <c r="K9" s="2">
         <f t="shared" si="2"/>
         <v>400</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L9" s="2">
+      <c r="L9" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M9" s="2">
         <v>2</v>
       </c>
-      <c r="M9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N9" s="2">
+      <c r="N9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O9" s="2">
         <v>100002</v>
       </c>
-      <c r="P9" s="2" t="b">
+      <c r="Q9" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="R9" s="2">
         <v>0</v>
       </c>
-      <c r="R9" s="1" t="s">
-        <v>40</v>
+      <c r="S9" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:19">
       <c r="A10" s="2">
         <v>30020012</v>
       </c>
@@ -1786,7 +1817,7 @@
         <v>300200</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -1798,44 +1829,47 @@
         <v>60000</v>
       </c>
       <c r="G10" s="2">
+        <v>16008</v>
+      </c>
+      <c r="H10" s="2">
         <f t="shared" si="0"/>
         <v>40000</v>
       </c>
-      <c r="H10" s="2">
+      <c r="I10" s="2">
         <v>0</v>
       </c>
-      <c r="I10" s="2">
+      <c r="J10" s="2">
         <f t="shared" si="1"/>
         <v>500</v>
       </c>
-      <c r="J10" s="2">
+      <c r="K10" s="2">
         <f t="shared" si="2"/>
         <v>1000</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="L10" s="2">
+      <c r="L10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="M10" s="2">
         <v>2</v>
       </c>
-      <c r="M10" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="N10" s="2">
+      <c r="N10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="O10" s="2">
         <v>100002</v>
       </c>
-      <c r="P10" s="2" t="b">
+      <c r="Q10" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="R10" s="2">
         <v>0</v>
       </c>
-      <c r="R10" s="1" t="s">
-        <v>40</v>
+      <c r="S10" s="1" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:R10" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:S10" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/poker/resources/sample/Texas.xlsx
+++ b/poker/resources/sample/Texas.xlsx
@@ -1528,7 +1528,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="2">
-        <v>2000000</v>
+        <v>1000</v>
       </c>
       <c r="F5" s="2">
         <v>60000</v>
@@ -1538,18 +1538,18 @@
       </c>
       <c r="H5" s="2">
         <f t="shared" ref="H5:H10" si="0">E5*2</f>
-        <v>4000000</v>
+        <v>2000</v>
       </c>
       <c r="I5" s="2">
         <v>0</v>
       </c>
       <c r="J5" s="2">
         <f t="shared" ref="J5:J10" si="1">K5/2</f>
-        <v>50000</v>
+        <v>25</v>
       </c>
       <c r="K5" s="2">
-        <f t="shared" ref="K5:K10" si="2">E5/20</f>
-        <v>100000</v>
+        <f>E5/20</f>
+        <v>50</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>40</v>
@@ -1587,7 +1587,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="2">
-        <v>4000000</v>
+        <v>100000</v>
       </c>
       <c r="F6" s="2">
         <v>60000</v>
@@ -1597,18 +1597,18 @@
       </c>
       <c r="H6" s="2">
         <f t="shared" si="0"/>
-        <v>8000000</v>
+        <v>200000</v>
       </c>
       <c r="I6" s="2">
         <v>0</v>
       </c>
       <c r="J6" s="2">
         <f t="shared" si="1"/>
-        <v>100000</v>
+        <v>2500</v>
       </c>
       <c r="K6" s="2">
-        <f t="shared" si="2"/>
-        <v>200000</v>
+        <f t="shared" ref="K5:K10" si="2">E6/20</f>
+        <v>5000</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>40</v>
@@ -1646,7 +1646,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="2">
-        <v>20000000</v>
+        <v>10000000</v>
       </c>
       <c r="F7" s="2">
         <v>60000</v>
@@ -1656,18 +1656,18 @@
       </c>
       <c r="H7" s="2">
         <f t="shared" si="0"/>
-        <v>40000000</v>
+        <v>20000000</v>
       </c>
       <c r="I7" s="2">
         <v>0</v>
       </c>
       <c r="J7" s="2">
         <f t="shared" si="1"/>
-        <v>500000</v>
+        <v>250000</v>
       </c>
       <c r="K7" s="2">
         <f t="shared" si="2"/>
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>40</v>
@@ -1705,7 +1705,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="2">
-        <v>2000</v>
+        <v>40</v>
       </c>
       <c r="F8" s="2">
         <v>60000</v>
@@ -1715,18 +1715,18 @@
       </c>
       <c r="H8" s="2">
         <f t="shared" si="0"/>
-        <v>4000</v>
+        <v>80</v>
       </c>
       <c r="I8" s="2">
         <v>0</v>
       </c>
       <c r="J8" s="2">
         <f t="shared" si="1"/>
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="K8" s="2">
         <f t="shared" si="2"/>
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>40</v>
@@ -1764,7 +1764,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="2">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="F9" s="2">
         <v>60000</v>
@@ -1774,18 +1774,18 @@
       </c>
       <c r="H9" s="2">
         <f t="shared" si="0"/>
-        <v>16000</v>
+        <v>8000</v>
       </c>
       <c r="I9" s="2">
         <v>0</v>
       </c>
       <c r="J9" s="2">
         <f t="shared" si="1"/>
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="K9" s="2">
         <f t="shared" si="2"/>
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>40</v>
@@ -1823,7 +1823,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="2">
-        <v>20000</v>
+        <v>400000</v>
       </c>
       <c r="F10" s="2">
         <v>60000</v>
@@ -1833,18 +1833,18 @@
       </c>
       <c r="H10" s="2">
         <f t="shared" si="0"/>
-        <v>40000</v>
+        <v>800000</v>
       </c>
       <c r="I10" s="2">
         <v>0</v>
       </c>
       <c r="J10" s="2">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>10000</v>
       </c>
       <c r="K10" s="2">
         <f t="shared" si="2"/>
-        <v>1000</v>
+        <v>20000</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>40</v>

--- a/poker/resources/sample/Texas.xlsx
+++ b/poker/resources/sample/Texas.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Texas" sheetId="47" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Texas!$B$1:$S$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Texas!$B$1:$Q$10</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +60,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="1">
+    <comment ref="G1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -82,7 +82,19 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="1">
+    <comment ref="H1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>单位：K</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -102,24 +114,12 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>单位：K</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M1" authorId="1">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
           <t>1 先跟再加
 2 直接加</t>
         </r>
       </text>
     </comment>
-    <comment ref="P1" authorId="2">
+    <comment ref="N1" authorId="2">
       <text>
         <r>
           <rPr>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="39">
   <si>
     <t>id</t>
   </si>
@@ -156,12 +156,6 @@
     <t>默认入座金币</t>
   </si>
   <si>
-    <t>请离房间（毫秒）</t>
-  </si>
-  <si>
-    <t>踢出房间提示</t>
-  </si>
-  <si>
     <t>上桌金额</t>
   </si>
   <si>
@@ -217,12 +211,6 @@
   </si>
   <si>
     <t>coinsNum</t>
-  </si>
-  <si>
-    <t>escTime</t>
-  </si>
-  <si>
-    <t>escTipText</t>
   </si>
   <si>
     <t>tablecoin</t>
@@ -978,11 +966,11 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1321,30 +1309,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.375" style="2" customWidth="1"/>
     <col min="2" max="2" width="12" style="2" customWidth="1"/>
     <col min="3" max="3" width="17.5" style="2" customWidth="1"/>
     <col min="4" max="4" width="9.625" style="2" customWidth="1"/>
-    <col min="5" max="7" width="28.625" style="2" customWidth="1"/>
-    <col min="8" max="8" width="19.725" style="2" customWidth="1"/>
-    <col min="9" max="9" width="9.25" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9" style="2"/>
-    <col min="11" max="11" width="9.25" style="2"/>
-    <col min="12" max="12" width="16.875" style="2" customWidth="1"/>
-    <col min="13" max="13" width="19.75" style="2" customWidth="1"/>
-    <col min="14" max="14" width="22.5" style="2" customWidth="1"/>
-    <col min="15" max="15" width="9" style="2"/>
-    <col min="16" max="16" width="24.75" style="2" customWidth="1"/>
-    <col min="17" max="17" width="11.25" style="2" customWidth="1"/>
-    <col min="18" max="18" width="9.25" style="2" customWidth="1"/>
-    <col min="19" max="19" width="15" style="2" customWidth="1"/>
-    <col min="20" max="16384" width="9" style="2"/>
+    <col min="5" max="5" width="28.625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19.725" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.25" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9" style="2"/>
+    <col min="9" max="9" width="9.25" style="2"/>
+    <col min="10" max="10" width="16.875" style="2" customWidth="1"/>
+    <col min="11" max="11" width="19.75" style="2" customWidth="1"/>
+    <col min="12" max="12" width="22.5" style="2" customWidth="1"/>
+    <col min="13" max="13" width="9" style="2"/>
+    <col min="14" max="14" width="24.75" style="2" customWidth="1"/>
+    <col min="15" max="15" width="11.25" style="2" customWidth="1"/>
+    <col min="16" max="16" width="9.25" style="2" customWidth="1"/>
+    <col min="17" max="17" width="15" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:17">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1360,161 +1348,141 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="P1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="9" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:16">
+      <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="K2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:18">
-      <c r="A2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:18">
+    <row r="3" s="1" customFormat="1" spans="1:16">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="O3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>38</v>
-      </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="5:7">
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
+    <row r="4" s="1" customFormat="1" spans="5:5">
+      <c r="E4" s="7"/>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:17">
       <c r="A5" s="2">
         <v>3002001</v>
       </c>
@@ -1522,7 +1490,7 @@
         <v>300200</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
@@ -1531,49 +1499,43 @@
         <v>1000</v>
       </c>
       <c r="F5" s="2">
-        <v>60000</v>
+        <f t="shared" ref="F5:F10" si="0">E5*2</f>
+        <v>2000</v>
       </c>
       <c r="G5" s="2">
-        <v>16008</v>
+        <v>0</v>
       </c>
       <c r="H5" s="2">
-        <f t="shared" ref="H5:H10" si="0">E5*2</f>
-        <v>2000</v>
+        <f t="shared" ref="H5:H10" si="1">I5/2</f>
+        <v>25</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
-      </c>
-      <c r="J5" s="2">
-        <f t="shared" ref="J5:J10" si="1">K5/2</f>
-        <v>25</v>
-      </c>
-      <c r="K5" s="2">
         <f>E5/20</f>
         <v>50</v>
       </c>
+      <c r="J5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="2">
+        <v>2</v>
+      </c>
       <c r="L5" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="M5" s="2">
-        <v>2</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="O5" s="2">
         <v>100002</v>
       </c>
-      <c r="Q5" s="2" t="b">
+      <c r="O5" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="R5" s="2">
+      <c r="P5" s="2">
         <v>0</v>
       </c>
-      <c r="S5" s="1" t="s">
-        <v>42</v>
+      <c r="Q5" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:17">
       <c r="A6" s="2">
         <v>3002002</v>
       </c>
@@ -1581,7 +1543,7 @@
         <v>300200</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
@@ -1590,49 +1552,43 @@
         <v>100000</v>
       </c>
       <c r="F6" s="2">
-        <v>60000</v>
-      </c>
-      <c r="G6" s="2">
-        <v>16008</v>
-      </c>
-      <c r="H6" s="2">
         <f t="shared" si="0"/>
         <v>200000</v>
       </c>
-      <c r="I6" s="2">
+      <c r="G6" s="2">
         <v>0</v>
       </c>
-      <c r="J6" s="2">
+      <c r="H6" s="2">
         <f t="shared" si="1"/>
         <v>2500</v>
       </c>
+      <c r="I6" s="2">
+        <f t="shared" ref="I5:I10" si="2">E6/20</f>
+        <v>5000</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>36</v>
+      </c>
       <c r="K6" s="2">
-        <f t="shared" ref="K5:K10" si="2">E6/20</f>
-        <v>5000</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="M6" s="2">
-        <v>2</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="O6" s="2">
         <v>100002</v>
       </c>
-      <c r="Q6" s="2" t="b">
+      <c r="O6" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="R6" s="2">
+      <c r="P6" s="2">
         <v>0</v>
       </c>
-      <c r="S6" s="1" t="s">
-        <v>42</v>
+      <c r="Q6" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:17">
       <c r="A7" s="2">
         <v>3002003</v>
       </c>
@@ -1640,7 +1596,7 @@
         <v>300200</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -1649,49 +1605,43 @@
         <v>10000000</v>
       </c>
       <c r="F7" s="2">
-        <v>60000</v>
-      </c>
-      <c r="G7" s="2">
-        <v>16008</v>
-      </c>
-      <c r="H7" s="2">
         <f t="shared" si="0"/>
         <v>20000000</v>
       </c>
-      <c r="I7" s="2">
+      <c r="G7" s="2">
         <v>0</v>
       </c>
-      <c r="J7" s="2">
+      <c r="H7" s="2">
         <f t="shared" si="1"/>
         <v>250000</v>
       </c>
-      <c r="K7" s="2">
+      <c r="I7" s="2">
         <f t="shared" si="2"/>
         <v>500000</v>
       </c>
+      <c r="J7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K7" s="2">
+        <v>2</v>
+      </c>
       <c r="L7" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="M7" s="2">
-        <v>2</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="O7" s="2">
         <v>100002</v>
       </c>
-      <c r="Q7" s="2" t="b">
+      <c r="O7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="R7" s="2">
+      <c r="P7" s="2">
         <v>0</v>
       </c>
-      <c r="S7" s="1" t="s">
-        <v>42</v>
+      <c r="Q7" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:17">
       <c r="A8" s="2">
         <v>30020010</v>
       </c>
@@ -1699,7 +1649,7 @@
         <v>300200</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D8" s="1">
         <v>1</v>
@@ -1708,49 +1658,43 @@
         <v>40</v>
       </c>
       <c r="F8" s="2">
-        <v>60000</v>
-      </c>
-      <c r="G8" s="2">
-        <v>16008</v>
-      </c>
-      <c r="H8" s="2">
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="I8" s="2">
+      <c r="G8" s="2">
         <v>0</v>
       </c>
-      <c r="J8" s="2">
+      <c r="H8" s="2">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="K8" s="2">
+      <c r="I8" s="2">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
+      <c r="J8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" s="2">
+        <v>2</v>
+      </c>
       <c r="L8" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="M8" s="2">
-        <v>2</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="O8" s="2">
         <v>100002</v>
       </c>
-      <c r="Q8" s="2" t="b">
+      <c r="O8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="R8" s="2">
+      <c r="P8" s="2">
         <v>0</v>
       </c>
-      <c r="S8" s="1" t="s">
-        <v>42</v>
+      <c r="Q8" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:17">
       <c r="A9" s="2">
         <v>30020011</v>
       </c>
@@ -1758,7 +1702,7 @@
         <v>300200</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
@@ -1767,49 +1711,43 @@
         <v>4000</v>
       </c>
       <c r="F9" s="2">
-        <v>60000</v>
-      </c>
-      <c r="G9" s="2">
-        <v>16008</v>
-      </c>
-      <c r="H9" s="2">
         <f t="shared" si="0"/>
         <v>8000</v>
       </c>
-      <c r="I9" s="2">
+      <c r="G9" s="2">
         <v>0</v>
       </c>
-      <c r="J9" s="2">
+      <c r="H9" s="2">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="K9" s="2">
+      <c r="I9" s="2">
         <f t="shared" si="2"/>
         <v>200</v>
       </c>
+      <c r="J9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9" s="2">
+        <v>2</v>
+      </c>
       <c r="L9" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="M9" s="2">
-        <v>2</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="O9" s="2">
         <v>100002</v>
       </c>
-      <c r="Q9" s="2" t="b">
+      <c r="O9" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="R9" s="2">
+      <c r="P9" s="2">
         <v>0</v>
       </c>
-      <c r="S9" s="1" t="s">
-        <v>42</v>
+      <c r="Q9" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:17">
       <c r="A10" s="2">
         <v>30020012</v>
       </c>
@@ -1817,7 +1755,7 @@
         <v>300200</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -1826,50 +1764,44 @@
         <v>400000</v>
       </c>
       <c r="F10" s="2">
-        <v>60000</v>
-      </c>
-      <c r="G10" s="2">
-        <v>16008</v>
-      </c>
-      <c r="H10" s="2">
         <f t="shared" si="0"/>
         <v>800000</v>
       </c>
-      <c r="I10" s="2">
+      <c r="G10" s="2">
         <v>0</v>
       </c>
-      <c r="J10" s="2">
+      <c r="H10" s="2">
         <f t="shared" si="1"/>
         <v>10000</v>
       </c>
-      <c r="K10" s="2">
+      <c r="I10" s="2">
         <f t="shared" si="2"/>
         <v>20000</v>
       </c>
+      <c r="J10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K10" s="2">
+        <v>2</v>
+      </c>
       <c r="L10" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="M10" s="2">
-        <v>2</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="O10" s="2">
         <v>100002</v>
       </c>
-      <c r="Q10" s="2" t="b">
+      <c r="O10" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="R10" s="2">
+      <c r="P10" s="2">
         <v>0</v>
       </c>
-      <c r="S10" s="1" t="s">
-        <v>42</v>
+      <c r="Q10" s="1" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:S10" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B1:Q10" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/poker/resources/sample/Texas.xlsx
+++ b/poker/resources/sample/Texas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="824"/>
+    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="824"/>
   </bookViews>
   <sheets>
     <sheet name="Texas" sheetId="47" r:id="rId1"/>
@@ -57,6 +57,50 @@
           </rPr>
           <t>2 中级场
 3 高级场</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+坐下时要求的金额</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+每次游戏开始时放入的金额</t>
         </r>
       </text>
     </comment>
@@ -1496,21 +1540,21 @@
         <v>1</v>
       </c>
       <c r="E5" s="2">
+        <f t="shared" ref="E5:E10" si="0">F5*2</f>
+        <v>2000</v>
+      </c>
+      <c r="F5" s="2">
         <v>1000</v>
-      </c>
-      <c r="F5" s="2">
-        <f t="shared" ref="F5:F10" si="0">E5*2</f>
-        <v>2000</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="2">
-        <f t="shared" ref="H5:H10" si="1">I5/2</f>
+        <f>I5/2</f>
         <v>25</v>
       </c>
       <c r="I5" s="2">
-        <f>E5/20</f>
+        <f>F5/20</f>
         <v>50</v>
       </c>
       <c r="J5" s="2" t="s">
@@ -1549,21 +1593,21 @@
         <v>2</v>
       </c>
       <c r="E6" s="2">
-        <v>100000</v>
-      </c>
-      <c r="F6" s="2">
         <f t="shared" si="0"/>
         <v>200000</v>
       </c>
+      <c r="F6" s="2">
+        <v>100000</v>
+      </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="H5:H10" si="1">I6/2</f>
         <v>2500</v>
       </c>
       <c r="I6" s="2">
-        <f t="shared" ref="I5:I10" si="2">E6/20</f>
+        <f t="shared" ref="I5:I10" si="2">F6/20</f>
         <v>5000</v>
       </c>
       <c r="J6" s="2" t="s">
@@ -1602,11 +1646,11 @@
         <v>3</v>
       </c>
       <c r="E7" s="2">
-        <v>10000000</v>
-      </c>
-      <c r="F7" s="2">
         <f t="shared" si="0"/>
         <v>20000000</v>
+      </c>
+      <c r="F7" s="2">
+        <v>10000000</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
@@ -1655,11 +1699,11 @@
         <v>1</v>
       </c>
       <c r="E8" s="2">
-        <v>40</v>
-      </c>
-      <c r="F8" s="2">
         <f t="shared" si="0"/>
         <v>80</v>
+      </c>
+      <c r="F8" s="2">
+        <v>40</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
@@ -1708,11 +1752,11 @@
         <v>2</v>
       </c>
       <c r="E9" s="2">
-        <v>4000</v>
-      </c>
-      <c r="F9" s="2">
         <f t="shared" si="0"/>
         <v>8000</v>
+      </c>
+      <c r="F9" s="2">
+        <v>4000</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
@@ -1761,11 +1805,11 @@
         <v>3</v>
       </c>
       <c r="E10" s="2">
-        <v>400000</v>
-      </c>
-      <c r="F10" s="2">
         <f t="shared" si="0"/>
         <v>800000</v>
+      </c>
+      <c r="F10" s="2">
+        <v>400000</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>

--- a/poker/resources/sample/Texas.xlsx
+++ b/poker/resources/sample/Texas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="824"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="824"/>
   </bookViews>
   <sheets>
     <sheet name="Texas" sheetId="47" r:id="rId1"/>
@@ -1700,21 +1700,21 @@
       </c>
       <c r="E8" s="2">
         <f t="shared" si="0"/>
-        <v>80</v>
+        <v>400</v>
       </c>
       <c r="F8" s="2">
-        <v>40</v>
+        <v>200</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="2">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I8" s="2">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>36</v>
@@ -1753,21 +1753,21 @@
       </c>
       <c r="E9" s="2">
         <f t="shared" si="0"/>
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="F9" s="2">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="2">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="I9" s="2">
         <f t="shared" si="2"/>
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>36</v>
@@ -1806,21 +1806,21 @@
       </c>
       <c r="E10" s="2">
         <f t="shared" si="0"/>
-        <v>800000</v>
+        <v>200000</v>
       </c>
       <c r="F10" s="2">
-        <v>400000</v>
+        <v>100000</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
       </c>
       <c r="H10" s="2">
         <f t="shared" si="1"/>
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="I10" s="2">
         <f t="shared" si="2"/>
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>36</v>

--- a/poker/resources/sample/Texas.xlsx
+++ b/poker/resources/sample/Texas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="824"/>
+    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="824"/>
   </bookViews>
   <sheets>
     <sheet name="Texas" sheetId="47" r:id="rId1"/>
@@ -993,7 +993,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1013,14 +1013,17 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="61">
@@ -1419,17 +1422,17 @@
       <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="O1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="8" t="s">
         <v>15</v>
       </c>
       <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:16">
+    <row r="2" s="1" customFormat="1" spans="1:17">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -1476,7 +1479,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:16">
+    <row r="3" s="1" customFormat="1" spans="1:17">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1523,324 +1526,312 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="5:5">
-      <c r="E4" s="7"/>
+    <row r="4" s="1" customFormat="1" spans="1:17">
+      <c r="E4" s="9"/>
     </row>
     <row r="5" spans="1:17">
-      <c r="A5" s="2">
+      <c r="A5" s="10">
         <v>3002001</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="9">
         <v>300200</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="9">
         <v>1</v>
       </c>
-      <c r="E5" s="2">
-        <f t="shared" ref="E5:E10" si="0">F5*2</f>
-        <v>2000</v>
-      </c>
-      <c r="F5" s="2">
-        <v>1000</v>
-      </c>
-      <c r="G5" s="2">
+      <c r="E5" s="10">
+        <v>20000</v>
+      </c>
+      <c r="F5" s="10">
+        <v>10000</v>
+      </c>
+      <c r="G5" s="10">
         <v>0</v>
       </c>
-      <c r="H5" s="2">
-        <f>I5/2</f>
-        <v>25</v>
-      </c>
-      <c r="I5" s="2">
-        <f>F5/20</f>
-        <v>50</v>
-      </c>
-      <c r="J5" s="2" t="s">
+      <c r="H5" s="10">
+        <v>250</v>
+      </c>
+      <c r="I5" s="10">
+        <v>500</v>
+      </c>
+      <c r="J5" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5" s="10">
         <v>2</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="L5" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="M5" s="2">
+      <c r="M5" s="10">
         <v>100002</v>
       </c>
-      <c r="O5" s="2" t="b">
+      <c r="N5" s="10"/>
+      <c r="O5" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="10">
         <v>0</v>
       </c>
-      <c r="Q5" s="1" t="s">
+      <c r="Q5" s="9" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:17">
-      <c r="A6" s="2">
+      <c r="A6" s="10">
         <v>3002002</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="9">
         <v>300200</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="1">
+      <c r="D6" s="9">
         <v>2</v>
       </c>
-      <c r="E6" s="2">
-        <f t="shared" si="0"/>
+      <c r="E6" s="10">
         <v>200000</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="10">
         <v>100000</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="10">
         <v>0</v>
       </c>
-      <c r="H6" s="2">
-        <f t="shared" ref="H5:H10" si="1">I6/2</f>
+      <c r="H6" s="10">
         <v>2500</v>
       </c>
-      <c r="I6" s="2">
-        <f t="shared" ref="I5:I10" si="2">F6/20</f>
+      <c r="I6" s="10">
         <v>5000</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6" s="10">
         <v>2</v>
       </c>
-      <c r="L6" s="2" t="s">
+      <c r="L6" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="M6" s="2">
+      <c r="M6" s="10">
         <v>100002</v>
       </c>
-      <c r="O6" s="2" t="b">
+      <c r="N6" s="10"/>
+      <c r="O6" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="10">
         <v>0</v>
       </c>
-      <c r="Q6" s="1" t="s">
+      <c r="Q6" s="9" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:17">
-      <c r="A7" s="2">
+      <c r="A7" s="10">
         <v>3002003</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="9">
         <v>300200</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D7" s="9">
         <v>3</v>
       </c>
-      <c r="E7" s="2">
-        <f t="shared" si="0"/>
+      <c r="E7" s="10">
         <v>20000000</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="10">
         <v>10000000</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="10">
         <v>0</v>
       </c>
-      <c r="H7" s="2">
-        <f t="shared" si="1"/>
+      <c r="H7" s="10">
         <v>250000</v>
       </c>
-      <c r="I7" s="2">
-        <f t="shared" si="2"/>
+      <c r="I7" s="10">
         <v>500000</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="10">
         <v>2</v>
       </c>
-      <c r="L7" s="2" t="s">
+      <c r="L7" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="M7" s="2">
+      <c r="M7" s="10">
         <v>100002</v>
       </c>
-      <c r="O7" s="2" t="b">
+      <c r="N7" s="10"/>
+      <c r="O7" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="10">
         <v>0</v>
       </c>
-      <c r="Q7" s="1" t="s">
+      <c r="Q7" s="9" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:17">
-      <c r="A8" s="2">
+      <c r="A8" s="10">
         <v>30020010</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="9">
         <v>300200</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D8" s="9">
         <v>1</v>
       </c>
-      <c r="E8" s="2">
-        <f t="shared" si="0"/>
-        <v>400</v>
-      </c>
-      <c r="F8" s="2">
-        <v>200</v>
-      </c>
-      <c r="G8" s="2">
+      <c r="E8" s="10">
+        <v>20000</v>
+      </c>
+      <c r="F8" s="10">
+        <v>10000</v>
+      </c>
+      <c r="G8" s="10">
         <v>0</v>
       </c>
-      <c r="H8" s="2">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-      <c r="I8" s="2">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="J8" s="2" t="s">
+      <c r="H8" s="10">
+        <v>250</v>
+      </c>
+      <c r="I8" s="10">
+        <v>500</v>
+      </c>
+      <c r="J8" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" s="10">
         <v>2</v>
       </c>
-      <c r="L8" s="2" t="s">
+      <c r="L8" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="M8" s="2">
+      <c r="M8" s="10">
         <v>100002</v>
       </c>
-      <c r="O8" s="2" t="b">
+      <c r="N8" s="10"/>
+      <c r="O8" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="10">
         <v>0</v>
       </c>
-      <c r="Q8" s="1" t="s">
+      <c r="Q8" s="9" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:17">
-      <c r="A9" s="2">
+      <c r="A9" s="10">
         <v>30020011</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="9">
         <v>300200</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D9" s="9">
         <v>2</v>
       </c>
-      <c r="E9" s="2">
-        <f t="shared" si="0"/>
-        <v>10000</v>
-      </c>
-      <c r="F9" s="2">
+      <c r="E9" s="10">
+        <v>200000</v>
+      </c>
+      <c r="F9" s="10">
+        <v>100000</v>
+      </c>
+      <c r="G9" s="10">
+        <v>0</v>
+      </c>
+      <c r="H9" s="10">
+        <v>2500</v>
+      </c>
+      <c r="I9" s="10">
         <v>5000</v>
       </c>
-      <c r="G9" s="2">
+      <c r="J9" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9" s="10">
+        <v>2</v>
+      </c>
+      <c r="L9" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="M9" s="10">
+        <v>100002</v>
+      </c>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="P9" s="10">
         <v>0</v>
       </c>
-      <c r="H9" s="2">
-        <f t="shared" si="1"/>
-        <v>125</v>
-      </c>
-      <c r="I9" s="2">
-        <f t="shared" si="2"/>
-        <v>250</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="K9" s="2">
-        <v>2</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="M9" s="2">
-        <v>100002</v>
-      </c>
-      <c r="O9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P9" s="2">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="1" t="s">
+      <c r="Q9" s="9" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:17">
-      <c r="A10" s="2">
+      <c r="A10" s="10">
         <v>30020012</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="9">
         <v>300200</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="1">
+      <c r="D10" s="9">
         <v>3</v>
       </c>
-      <c r="E10" s="2">
-        <f t="shared" si="0"/>
-        <v>200000</v>
-      </c>
-      <c r="F10" s="2">
-        <v>100000</v>
-      </c>
-      <c r="G10" s="2">
+      <c r="E10" s="10">
+        <v>20000000</v>
+      </c>
+      <c r="F10" s="10">
+        <v>10000000</v>
+      </c>
+      <c r="G10" s="10">
         <v>0</v>
       </c>
-      <c r="H10" s="2">
-        <f t="shared" si="1"/>
-        <v>2500</v>
-      </c>
-      <c r="I10" s="2">
-        <f t="shared" si="2"/>
-        <v>5000</v>
-      </c>
-      <c r="J10" s="2" t="s">
+      <c r="H10" s="10">
+        <v>250000</v>
+      </c>
+      <c r="I10" s="10">
+        <v>500000</v>
+      </c>
+      <c r="J10" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10" s="10">
         <v>2</v>
       </c>
-      <c r="L10" s="2" t="s">
+      <c r="L10" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="M10" s="2">
+      <c r="M10" s="10">
         <v>100002</v>
       </c>
-      <c r="O10" s="2" t="b">
+      <c r="N10" s="10"/>
+      <c r="O10" s="10" t="b">
         <v>1</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="10">
         <v>0</v>
       </c>
-      <c r="Q10" s="1" t="s">
+      <c r="Q10" s="9" t="s">
         <v>38</v>
       </c>
     </row>

--- a/poker/resources/sample/Texas.xlsx
+++ b/poker/resources/sample/Texas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="824"/>
+    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="824"/>
   </bookViews>
   <sheets>
     <sheet name="Texas" sheetId="47" r:id="rId1"/>
@@ -482,12 +482,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1645,10 +1645,10 @@
         <v>3</v>
       </c>
       <c r="E7" s="10">
-        <v>20000000</v>
+        <v>2000000</v>
       </c>
       <c r="F7" s="10">
-        <v>10000000</v>
+        <v>1000000</v>
       </c>
       <c r="G7" s="10">
         <v>0</v>
@@ -1696,10 +1696,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="10">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="F8" s="10">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="G8" s="10">
         <v>0</v>
@@ -1747,10 +1747,10 @@
         <v>2</v>
       </c>
       <c r="E9" s="10">
-        <v>200000</v>
+        <v>0</v>
       </c>
       <c r="F9" s="10">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G9" s="10">
         <v>0</v>
@@ -1798,10 +1798,10 @@
         <v>3</v>
       </c>
       <c r="E10" s="10">
-        <v>20000000</v>
+        <v>0</v>
       </c>
       <c r="F10" s="10">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="G10" s="10">
         <v>0</v>

--- a/poker/resources/sample/Texas.xlsx
+++ b/poker/resources/sample/Texas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="824"/>
+    <workbookView windowWidth="27945" windowHeight="11925" tabRatio="824"/>
   </bookViews>
   <sheets>
     <sheet name="Texas" sheetId="47" r:id="rId1"/>
@@ -482,12 +482,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1696,10 +1696,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="10">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="F8" s="10">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G8" s="10">
         <v>0</v>
@@ -1747,10 +1747,10 @@
         <v>2</v>
       </c>
       <c r="E9" s="10">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="F9" s="10">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G9" s="10">
         <v>0</v>
@@ -1798,10 +1798,10 @@
         <v>3</v>
       </c>
       <c r="E10" s="10">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="F10" s="10">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="G10" s="10">
         <v>0</v>

--- a/poker/resources/sample/Texas.xlsx
+++ b/poker/resources/sample/Texas.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="824"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="824"/>
   </bookViews>
   <sheets>
     <sheet name="Texas" sheetId="47" r:id="rId1"/>
@@ -1696,10 +1696,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="10">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="F8" s="10">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="G8" s="10">
         <v>0</v>
@@ -1747,10 +1747,10 @@
         <v>2</v>
       </c>
       <c r="E9" s="10">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="F9" s="10">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G9" s="10">
         <v>0</v>
@@ -1798,10 +1798,10 @@
         <v>3</v>
       </c>
       <c r="E10" s="10">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="F10" s="10">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="G10" s="10">
         <v>0</v>

--- a/poker/resources/sample/Texas.xlsx
+++ b/poker/resources/sample/Texas.xlsx
@@ -1654,10 +1654,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="10">
-        <v>250000</v>
+        <v>25000</v>
       </c>
       <c r="I7" s="10">
-        <v>500000</v>
+        <v>50000</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>36</v>
@@ -1807,10 +1807,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="10">
-        <v>250000</v>
+        <v>25000</v>
       </c>
       <c r="I10" s="10">
-        <v>500000</v>
+        <v>50000</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>36</v>

--- a/poker/resources/sample/Texas.xlsx
+++ b/poker/resources/sample/Texas.xlsx
@@ -1654,10 +1654,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="10">
-        <v>25000</v>
+        <v>250000</v>
       </c>
       <c r="I7" s="10">
-        <v>50000</v>
+        <v>500000</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>36</v>
@@ -1807,10 +1807,10 @@
         <v>0</v>
       </c>
       <c r="H10" s="10">
-        <v>25000</v>
+        <v>250000</v>
       </c>
       <c r="I10" s="10">
-        <v>50000</v>
+        <v>500000</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>36</v>

--- a/poker/resources/sample/Texas.xlsx
+++ b/poker/resources/sample/Texas.xlsx
@@ -482,12 +482,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1543,19 +1543,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="10">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="F5" s="10">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="G5" s="10">
         <v>0</v>
       </c>
       <c r="H5" s="10">
-        <v>250</v>
+        <v>25</v>
       </c>
       <c r="I5" s="10">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="J5" s="10" t="s">
         <v>36</v>
@@ -1594,19 +1594,19 @@
         <v>2</v>
       </c>
       <c r="E6" s="10">
-        <v>200000</v>
+        <v>20000</v>
       </c>
       <c r="F6" s="10">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="G6" s="10">
         <v>0</v>
       </c>
       <c r="H6" s="10">
-        <v>2500</v>
+        <v>250</v>
       </c>
       <c r="I6" s="10">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>36</v>
@@ -1645,19 +1645,19 @@
         <v>3</v>
       </c>
       <c r="E7" s="10">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="F7" s="10">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
       <c r="G7" s="10">
         <v>0</v>
       </c>
       <c r="H7" s="10">
-        <v>25000</v>
+        <v>2500</v>
       </c>
       <c r="I7" s="10">
-        <v>50000</v>
+        <v>5000</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>36</v>
@@ -1696,19 +1696,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="10">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="F8" s="10">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="G8" s="10">
         <v>0</v>
       </c>
       <c r="H8" s="10">
-        <v>250</v>
+        <v>25</v>
       </c>
       <c r="I8" s="10">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>36</v>
@@ -1747,19 +1747,19 @@
         <v>2</v>
       </c>
       <c r="E9" s="10">
-        <v>200000</v>
+        <v>20000</v>
       </c>
       <c r="F9" s="10">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="G9" s="10">
         <v>0</v>
       </c>
       <c r="H9" s="10">
-        <v>2500</v>
+        <v>250</v>
       </c>
       <c r="I9" s="10">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>36</v>
@@ -1798,19 +1798,19 @@
         <v>3</v>
       </c>
       <c r="E10" s="10">
-        <v>2000000</v>
+        <v>200000</v>
       </c>
       <c r="F10" s="10">
-        <v>1000000</v>
+        <v>100000</v>
       </c>
       <c r="G10" s="10">
         <v>0</v>
       </c>
       <c r="H10" s="10">
-        <v>25000</v>
+        <v>2500</v>
       </c>
       <c r="I10" s="10">
-        <v>50000</v>
+        <v>5000</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>36</v>

--- a/poker/resources/sample/Texas.xlsx
+++ b/poker/resources/sample/Texas.xlsx
@@ -482,12 +482,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1543,10 +1543,10 @@
         <v>1</v>
       </c>
       <c r="E5" s="10">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F5" s="10">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G5" s="10">
         <v>0</v>
@@ -1594,10 +1594,10 @@
         <v>2</v>
       </c>
       <c r="E6" s="10">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F6" s="10">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="G6" s="10">
         <v>0</v>
@@ -1645,10 +1645,10 @@
         <v>3</v>
       </c>
       <c r="E7" s="10">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F7" s="10">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G7" s="10">
         <v>0</v>
@@ -1696,10 +1696,10 @@
         <v>1</v>
       </c>
       <c r="E8" s="10">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="F8" s="10">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="G8" s="10">
         <v>0</v>
@@ -1747,10 +1747,10 @@
         <v>2</v>
       </c>
       <c r="E9" s="10">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="F9" s="10">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="G9" s="10">
         <v>0</v>
@@ -1798,10 +1798,10 @@
         <v>3</v>
       </c>
       <c r="E10" s="10">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="F10" s="10">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G10" s="10">
         <v>0</v>

--- a/poker/resources/sample/Texas.xlsx
+++ b/poker/resources/sample/Texas.xlsx
@@ -1543,19 +1543,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="10">
-        <v>20000</v>
+        <v>1000</v>
       </c>
       <c r="F5" s="10">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="G5" s="10">
         <v>0</v>
       </c>
       <c r="H5" s="10">
-        <v>250</v>
+        <v>25</v>
       </c>
       <c r="I5" s="10">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="J5" s="10" t="s">
         <v>36</v>
@@ -1594,19 +1594,19 @@
         <v>2</v>
       </c>
       <c r="E6" s="10">
-        <v>200000</v>
+        <v>10000</v>
       </c>
       <c r="F6" s="10">
-        <v>100000</v>
+        <v>5000</v>
       </c>
       <c r="G6" s="10">
         <v>0</v>
       </c>
       <c r="H6" s="10">
-        <v>2500</v>
+        <v>250</v>
       </c>
       <c r="I6" s="10">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>36</v>
@@ -1645,19 +1645,19 @@
         <v>3</v>
       </c>
       <c r="E7" s="10">
-        <v>2000000</v>
+        <v>100000</v>
       </c>
       <c r="F7" s="10">
-        <v>1000000</v>
+        <v>50000</v>
       </c>
       <c r="G7" s="10">
         <v>0</v>
       </c>
       <c r="H7" s="10">
-        <v>250000</v>
+        <v>2500</v>
       </c>
       <c r="I7" s="10">
-        <v>500000</v>
+        <v>5000</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>36</v>
@@ -1696,19 +1696,19 @@
         <v>1</v>
       </c>
       <c r="E8" s="10">
-        <v>20000</v>
+        <v>1000</v>
       </c>
       <c r="F8" s="10">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="G8" s="10">
         <v>0</v>
       </c>
       <c r="H8" s="10">
-        <v>250</v>
+        <v>25</v>
       </c>
       <c r="I8" s="10">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>36</v>
@@ -1747,19 +1747,19 @@
         <v>2</v>
       </c>
       <c r="E9" s="10">
-        <v>200000</v>
+        <v>10000</v>
       </c>
       <c r="F9" s="10">
-        <v>100000</v>
+        <v>5000</v>
       </c>
       <c r="G9" s="10">
         <v>0</v>
       </c>
       <c r="H9" s="10">
-        <v>2500</v>
+        <v>250</v>
       </c>
       <c r="I9" s="10">
-        <v>5000</v>
+        <v>500</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>36</v>
@@ -1798,19 +1798,19 @@
         <v>3</v>
       </c>
       <c r="E10" s="10">
-        <v>2000000</v>
+        <v>100000</v>
       </c>
       <c r="F10" s="10">
-        <v>1000000</v>
+        <v>50000</v>
       </c>
       <c r="G10" s="10">
         <v>0</v>
       </c>
       <c r="H10" s="10">
-        <v>250000</v>
+        <v>2500</v>
       </c>
       <c r="I10" s="10">
-        <v>500000</v>
+        <v>5000</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>36</v>
